--- a/foreNback/risultati.xlsx
+++ b/foreNback/risultati.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\segmentation\foreNback\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42A7BD9-6374-4AE9-9C24-DD21EDCF9A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAF60C5-D39C-48A2-BD26-D91383C6050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34575" yWindow="45" windowWidth="21675" windowHeight="14760" xr2:uid="{C111D639-DAC3-4116-B91A-4E53EB96B601}"/>
+    <workbookView xWindow="1788" yWindow="840" windowWidth="20844" windowHeight="12396" xr2:uid="{C111D639-DAC3-4116-B91A-4E53EB96B601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="56">
   <si>
     <t>M3/N1879</t>
   </si>
@@ -206,6 +206,27 @@
   </si>
   <si>
     <t>t.opt</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDUSTRY    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICRO       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINANCE     </t>
+  </si>
+  <si>
+    <t>Macro</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Micro</t>
   </si>
 </sst>
 </file>
@@ -261,9 +282,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -301,7 +322,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -407,7 +428,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -549,7 +570,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -558,473 +579,489 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CCDA6C-474B-4376-99E7-B5F6128828A3}">
   <dimension ref="A1:R75"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>45</v>
       </c>
       <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>46</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>47</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>48</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2">
         <v>144</v>
       </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
       <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
         <v>24092765.27462</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>266</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>40446</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>2</v>
       </c>
-      <c r="J2">
-        <f>ABS(I2-I40)</f>
+      <c r="K2">
+        <f>ABS(J2-J40)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3">
         <v>144</v>
       </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
       <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
         <v>8360752.5599300005</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>363</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>20441</v>
       </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
       <c r="J3">
-        <f t="shared" ref="J3:J37" si="0">ABS(I3-I41)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K37" si="0">ABS(J3-J41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4">
         <v>144</v>
       </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
       <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
         <v>65136.19599</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>285</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>40027</v>
       </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
       <c r="J4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5">
         <v>144</v>
       </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
       <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
         <v>29611.05315</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>359</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>25539</v>
       </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
       <c r="J5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6">
         <v>144</v>
       </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
       <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <v>94746.701019999993</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>337</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>41697</v>
       </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
       <c r="J6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7">
         <v>144</v>
       </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
       <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
         <v>363787.27711999998</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>446</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>21688</v>
       </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
       <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8">
         <v>104</v>
       </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
       <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
         <v>194522.02369999999</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>219</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>12497</v>
       </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
       <c r="J8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9">
         <v>104</v>
       </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
       <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9">
         <v>6478704.1161000002</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>175</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>16713</v>
       </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
       <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10">
         <v>104</v>
       </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
       <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
         <v>67549187.476490006</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>160</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>19533</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>4</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11">
         <v>104</v>
       </c>
-      <c r="C11">
-        <v>6</v>
-      </c>
       <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
         <v>14795269.08694</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>262</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>4184</v>
       </c>
-      <c r="I11">
-        <v>7</v>
-      </c>
       <c r="J11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12">
         <v>104</v>
       </c>
-      <c r="C12">
-        <v>6</v>
-      </c>
       <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
         <v>17208.08454</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>248</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>8600</v>
       </c>
-      <c r="I12">
-        <v>7</v>
-      </c>
       <c r="J12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13">
         <v>1006</v>
       </c>
-      <c r="C13">
-        <v>6</v>
-      </c>
       <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13">
         <v>3183769.6773299999</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>202</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>1572</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>28636452</v>
       </c>
-      <c r="I13">
-        <v>7</v>
-      </c>
       <c r="J13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" t="s">
-        <v>19</v>
-      </c>
-      <c r="N13">
-        <v>3125249.6995199998</v>
-      </c>
-      <c r="O13" t="s">
-        <v>20</v>
-      </c>
-      <c r="P13">
-        <v>7</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>3</v>
-      </c>
-      <c r="R13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14">
         <v>115</v>
       </c>
-      <c r="C14">
-        <v>6</v>
-      </c>
       <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
         <v>37100222.050489999</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
       <c r="F14">
         <v>0</v>
       </c>
@@ -1032,1744 +1069,2034 @@
         <v>0</v>
       </c>
       <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>17037</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15">
         <v>126</v>
       </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
       <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
         <v>335032.43112000002</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>105</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>11704</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>3</v>
       </c>
-      <c r="J15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16">
         <v>71</v>
       </c>
-      <c r="C16">
-        <v>6</v>
-      </c>
       <c r="D16">
+        <v>6</v>
+      </c>
+      <c r="E16">
         <v>14716823.892859999</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>92</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>2329</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>2</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17">
         <v>126</v>
       </c>
-      <c r="C17">
-        <v>6</v>
-      </c>
       <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
         <v>8785.9450400000005</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>252</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>17004</v>
       </c>
-      <c r="I17">
-        <v>7</v>
-      </c>
       <c r="J17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18">
         <v>123</v>
       </c>
-      <c r="C18">
-        <v>6</v>
-      </c>
       <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
         <v>4010354.9343300001</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>263</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>18127</v>
       </c>
-      <c r="I18">
-        <v>7</v>
-      </c>
       <c r="J18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19">
         <v>123</v>
       </c>
-      <c r="C19">
-        <v>6</v>
-      </c>
       <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19">
         <v>219756.92032</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>334</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>21332</v>
       </c>
-      <c r="I19">
-        <v>7</v>
-      </c>
       <c r="J19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20">
         <v>170</v>
       </c>
-      <c r="C20">
-        <v>6</v>
-      </c>
       <c r="D20">
+        <v>6</v>
+      </c>
+      <c r="E20">
         <v>93339232.134739995</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>519</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>103936</v>
       </c>
-      <c r="I20">
-        <v>7</v>
-      </c>
       <c r="J20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21">
         <v>738</v>
       </c>
-      <c r="C21">
-        <v>6</v>
-      </c>
       <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21">
         <v>676312.21311999997</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>40</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>2659</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>6424871</v>
       </c>
-      <c r="I21">
-        <v>7</v>
-      </c>
       <c r="J21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22">
         <v>866</v>
       </c>
-      <c r="C22">
-        <v>6</v>
-      </c>
       <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="E22">
         <v>1477454.6941199999</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>97</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>1809</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>16246274</v>
       </c>
-      <c r="I22">
-        <v>7</v>
-      </c>
       <c r="J22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23">
         <v>115</v>
       </c>
-      <c r="C23">
-        <v>6</v>
-      </c>
       <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23">
         <v>41866.811699999998</v>
       </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>102</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>18649</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>2</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24">
         <v>97</v>
       </c>
-      <c r="C24">
-        <v>6</v>
-      </c>
       <c r="D24">
+        <v>6</v>
+      </c>
+      <c r="E24">
         <v>343646.65677</v>
       </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
         <v>183</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>6872</v>
       </c>
-      <c r="I24">
-        <v>7</v>
-      </c>
       <c r="J24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25">
         <v>253</v>
       </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
       <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25">
         <v>136.17642000000001</v>
       </c>
-      <c r="E25">
-        <v>1</v>
+      <c r="F25">
+        <v>0</v>
       </c>
       <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>974</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>270239</v>
       </c>
-      <c r="I25">
-        <v>7</v>
-      </c>
       <c r="J25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26">
         <v>367</v>
       </c>
-      <c r="C26">
-        <v>6</v>
-      </c>
       <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26">
         <v>89853060.744139999</v>
       </c>
-      <c r="E26">
-        <v>3</v>
+      <c r="F26">
+        <v>2</v>
       </c>
       <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26">
         <v>1157</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>675562</v>
       </c>
-      <c r="I26">
-        <v>7</v>
-      </c>
       <c r="J26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>34</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27">
         <v>263</v>
       </c>
-      <c r="C27">
-        <v>6</v>
-      </c>
       <c r="D27">
+        <v>6</v>
+      </c>
+      <c r="E27">
         <v>4.0999999999999999E-4</v>
       </c>
-      <c r="E27">
-        <v>1</v>
+      <c r="F27">
+        <v>0</v>
       </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>903</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>364509</v>
       </c>
-      <c r="I27">
-        <v>7</v>
-      </c>
       <c r="J27">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>35</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28">
         <v>263</v>
       </c>
-      <c r="C28">
-        <v>6</v>
-      </c>
       <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28">
         <v>9.3000000000000005E-4</v>
       </c>
-      <c r="E28">
-        <v>1</v>
+      <c r="F28">
+        <v>0</v>
       </c>
       <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>507</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>264444</v>
       </c>
-      <c r="I28">
-        <v>7</v>
-      </c>
       <c r="J28">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>36</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29">
         <v>253</v>
       </c>
-      <c r="C29">
-        <v>6</v>
-      </c>
       <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="E29">
         <v>3.1502300000000001</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <v>719</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>185694</v>
       </c>
-      <c r="I29">
-        <v>7</v>
-      </c>
       <c r="J29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>37</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30">
         <v>253</v>
       </c>
-      <c r="C30">
-        <v>6</v>
-      </c>
       <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
         <v>5.7162300000000004</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>816</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>185572</v>
       </c>
-      <c r="I30">
-        <v>7</v>
-      </c>
       <c r="J30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>38</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31">
         <v>253</v>
       </c>
-      <c r="C31">
-        <v>6</v>
-      </c>
       <c r="D31">
+        <v>6</v>
+      </c>
+      <c r="E31">
         <v>9.2608300000000003</v>
       </c>
-      <c r="E31">
-        <v>1</v>
+      <c r="F31">
+        <v>0</v>
       </c>
       <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
         <v>618</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>354703</v>
       </c>
-      <c r="I31">
-        <v>7</v>
-      </c>
       <c r="J31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>39</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32">
         <v>263</v>
       </c>
-      <c r="C32">
-        <v>6</v>
-      </c>
       <c r="D32">
+        <v>6</v>
+      </c>
+      <c r="E32">
         <v>1.39E-3</v>
       </c>
-      <c r="E32">
-        <v>1</v>
+      <c r="F32">
+        <v>0</v>
       </c>
       <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>580</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>291430</v>
       </c>
-      <c r="I32">
-        <v>7</v>
-      </c>
       <c r="J32">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>40</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33">
         <v>253</v>
       </c>
-      <c r="C33">
-        <v>6</v>
-      </c>
       <c r="D33">
+        <v>6</v>
+      </c>
+      <c r="E33">
         <v>68.210800000000006</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>760</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>214249</v>
       </c>
-      <c r="I33">
-        <v>7</v>
-      </c>
       <c r="J33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>41</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34">
         <v>253</v>
       </c>
-      <c r="C34">
-        <v>6</v>
-      </c>
       <c r="D34">
+        <v>6</v>
+      </c>
+      <c r="E34">
         <v>61.307380000000002</v>
       </c>
-      <c r="E34">
-        <v>1</v>
+      <c r="F34">
+        <v>0</v>
       </c>
       <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>784</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>301279</v>
       </c>
-      <c r="I34">
-        <v>7</v>
-      </c>
       <c r="J34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>42</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35">
         <v>253</v>
       </c>
-      <c r="C35">
-        <v>6</v>
-      </c>
       <c r="D35">
+        <v>6</v>
+      </c>
+      <c r="E35">
         <v>84.234819999999999</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>824</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>225076</v>
       </c>
-      <c r="I35">
-        <v>7</v>
-      </c>
       <c r="J35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>43</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36">
         <v>253</v>
       </c>
-      <c r="C36">
-        <v>6</v>
-      </c>
       <c r="D36">
+        <v>6</v>
+      </c>
+      <c r="E36">
         <v>7.59185</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0</v>
       </c>
       <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>686</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>132486</v>
       </c>
-      <c r="I36">
-        <v>7</v>
-      </c>
       <c r="J36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>44</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37">
         <v>263</v>
       </c>
-      <c r="C37">
-        <v>6</v>
-      </c>
       <c r="D37">
+        <v>6</v>
+      </c>
+      <c r="E37">
         <v>29.102270000000001</v>
       </c>
-      <c r="E37">
-        <v>1</v>
+      <c r="F37">
+        <v>0</v>
       </c>
       <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <v>687</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>263442</v>
       </c>
-      <c r="I37">
-        <v>7</v>
-      </c>
       <c r="J37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>45</v>
       </c>
       <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
         <v>1</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>2</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>46</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>47</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>48</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>4</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>5</v>
       </c>
-      <c r="I39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>0</v>
       </c>
-      <c r="B40">
-        <f>B37</f>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40">
+        <f>C37</f>
         <v>263</v>
       </c>
-      <c r="C40">
-        <v>8</v>
-      </c>
       <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40">
         <v>2025.1802</v>
       </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>362</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>7174</v>
       </c>
-      <c r="I40">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>7</v>
       </c>
-      <c r="B41">
-        <f>B40</f>
+      <c r="B41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:C50" si="1">C40</f>
         <v>263</v>
       </c>
-      <c r="C41">
-        <v>8</v>
-      </c>
       <c r="D41">
+        <v>8</v>
+      </c>
+      <c r="E41">
         <v>1819.64571</v>
       </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>355</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>11831</v>
       </c>
-      <c r="I41">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>8</v>
       </c>
-      <c r="B42">
-        <f>B41</f>
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="C42">
-        <v>8</v>
-      </c>
       <c r="D42">
+        <v>8</v>
+      </c>
+      <c r="E42">
         <v>1108.90806</v>
       </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>425</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>20198</v>
       </c>
-      <c r="I42">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J42">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B43">
-        <f>B42</f>
+      <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="C43">
-        <v>8</v>
-      </c>
       <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43">
         <v>976.01432</v>
       </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
         <v>431</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>20765</v>
       </c>
-      <c r="I43">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>10</v>
       </c>
-      <c r="B44">
-        <f>B43</f>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="C44">
-        <v>8</v>
-      </c>
       <c r="D44">
+        <v>8</v>
+      </c>
+      <c r="E44">
         <v>1119.5927099999999</v>
       </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
         <v>437</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>13336</v>
       </c>
-      <c r="I44">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>11</v>
       </c>
-      <c r="B45">
-        <f>B44</f>
+      <c r="B45" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="C45">
-        <v>8</v>
-      </c>
       <c r="D45">
+        <v>8</v>
+      </c>
+      <c r="E45">
         <v>1395.69139</v>
       </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
         <v>401</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>16108</v>
       </c>
-      <c r="I45">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>12</v>
       </c>
-      <c r="B46">
-        <f>B45</f>
+      <c r="B46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="C46">
-        <v>8</v>
-      </c>
       <c r="D46">
+        <v>8</v>
+      </c>
+      <c r="E46">
         <v>959.84159999999997</v>
       </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>237</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>6173</v>
       </c>
-      <c r="I46">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>13</v>
       </c>
-      <c r="B47">
-        <f>B46</f>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="C47">
-        <v>8</v>
-      </c>
       <c r="D47">
+        <v>8</v>
+      </c>
+      <c r="E47">
         <v>1289.78763</v>
       </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>269</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>6088</v>
       </c>
-      <c r="I47">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J47">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>14</v>
       </c>
-      <c r="B48">
-        <f>B47</f>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="C48">
-        <v>8</v>
-      </c>
       <c r="D48">
+        <v>8</v>
+      </c>
+      <c r="E48">
         <v>1580.99199</v>
       </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
         <v>171</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>2953</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>15</v>
       </c>
-      <c r="B49">
-        <f>B48</f>
+      <c r="B49" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="C49">
-        <v>8</v>
-      </c>
       <c r="D49">
+        <v>8</v>
+      </c>
+      <c r="E49">
         <v>1391.7179799999999</v>
       </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
         <v>240</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>4093</v>
       </c>
-      <c r="I49">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>16</v>
       </c>
-      <c r="B50">
-        <f>B49</f>
+      <c r="B50" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="C50">
-        <v>8</v>
-      </c>
       <c r="D50">
+        <v>8</v>
+      </c>
+      <c r="E50">
         <v>707.71519000000001</v>
       </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
       <c r="F50">
         <v>0</v>
       </c>
       <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
         <v>229</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>6110</v>
       </c>
-      <c r="I50">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>17</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51">
         <v>1006</v>
       </c>
-      <c r="C51">
-        <v>8</v>
-      </c>
       <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
         <v>10587.689979999999</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>71</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>2055</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>4883838</v>
       </c>
-      <c r="I51">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J51">
+        <v>7</v>
+      </c>
+      <c r="K51" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" t="s">
+        <v>17</v>
+      </c>
+      <c r="M51" t="s">
+        <v>19</v>
+      </c>
+      <c r="N51">
+        <v>3125249.6995199998</v>
+      </c>
+      <c r="O51" t="s">
+        <v>20</v>
+      </c>
+      <c r="P51">
+        <v>7</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>3</v>
+      </c>
+      <c r="R51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>21</v>
       </c>
-      <c r="B52">
-        <f>B51</f>
-        <v>1006</v>
+      <c r="B52" t="s">
+        <v>50</v>
       </c>
       <c r="C52">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="D52">
+        <v>8</v>
+      </c>
+      <c r="E52">
         <v>1730.1180300000001</v>
       </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="G52">
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="H52">
         <v>80</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>1213</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>22</v>
       </c>
-      <c r="B53">
+      <c r="B53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53">
         <v>126</v>
       </c>
-      <c r="C53">
-        <v>8</v>
-      </c>
       <c r="D53">
+        <v>8</v>
+      </c>
+      <c r="E53">
         <v>1228.21128</v>
       </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="G53">
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="H53">
         <v>125</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>6303</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>23</v>
       </c>
-      <c r="B54">
+      <c r="B54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54">
         <v>71</v>
       </c>
-      <c r="C54">
-        <v>8</v>
-      </c>
       <c r="D54">
+        <v>8</v>
+      </c>
+      <c r="E54">
         <v>977.77576999999997</v>
       </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="G54">
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>85</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>1123</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>24</v>
       </c>
-      <c r="B55">
+      <c r="B55" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55">
         <v>126</v>
       </c>
-      <c r="C55">
-        <v>8</v>
-      </c>
       <c r="D55">
+        <v>8</v>
+      </c>
+      <c r="E55">
         <v>723.20570999999995</v>
       </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="G55">
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="H55">
         <v>225</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>14281</v>
       </c>
-      <c r="I55">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J55">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>25</v>
       </c>
-      <c r="B56">
+      <c r="B56" t="s">
+        <v>50</v>
+      </c>
+      <c r="C56">
         <v>123</v>
       </c>
-      <c r="C56">
-        <v>8</v>
-      </c>
       <c r="D56">
+        <v>8</v>
+      </c>
+      <c r="E56">
         <v>1072.62167</v>
       </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="G56">
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="H56">
         <v>305</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>15793</v>
       </c>
-      <c r="I56">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J56">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>26</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="s">
+        <v>50</v>
+      </c>
+      <c r="C57">
         <v>123</v>
       </c>
-      <c r="C57">
-        <v>8</v>
-      </c>
-      <c r="D57" t="e" cm="1">
-        <f t="array" ref="D57">-inf</f>
+      <c r="D57">
+        <v>8</v>
+      </c>
+      <c r="E57" t="e" cm="1">
+        <f t="array" ref="E57">-inf</f>
         <v>#NAME?</v>
       </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="G57">
+      <c r="F57">
         <v>0</v>
       </c>
       <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
         <v>827</v>
       </c>
-      <c r="I57">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J57">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>27</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58">
         <v>170</v>
       </c>
-      <c r="C58">
-        <v>8</v>
-      </c>
       <c r="D58">
+        <v>8</v>
+      </c>
+      <c r="E58">
         <v>2563.7106699999999</v>
       </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="G58">
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="H58">
         <v>574</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>19364</v>
       </c>
-      <c r="I58">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J58">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>28</v>
       </c>
-      <c r="B59">
+      <c r="B59" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59">
         <v>738</v>
       </c>
-      <c r="C59">
-        <v>8</v>
-      </c>
       <c r="D59">
+        <v>8</v>
+      </c>
+      <c r="E59">
         <v>6547.8270499999999</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>28</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>1911</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>2785509</v>
       </c>
-      <c r="I59">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>29</v>
       </c>
-      <c r="B60">
+      <c r="B60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60">
         <v>866</v>
       </c>
-      <c r="C60">
-        <v>8</v>
-      </c>
       <c r="D60">
+        <v>8</v>
+      </c>
+      <c r="E60">
         <v>8097.7355600000001</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>38</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>2590</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>3831071</v>
       </c>
-      <c r="I60">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J60">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>30</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="s">
+        <v>55</v>
+      </c>
+      <c r="C61">
         <v>115</v>
       </c>
-      <c r="C61">
-        <v>8</v>
-      </c>
       <c r="D61">
+        <v>8</v>
+      </c>
+      <c r="E61">
         <v>916.15124000000003</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
         <v>222</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>3529</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>31</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62">
         <v>97</v>
       </c>
-      <c r="C62">
-        <v>8</v>
-      </c>
       <c r="D62">
+        <v>8</v>
+      </c>
+      <c r="E62">
         <v>943.33713</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>0</v>
       </c>
       <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
         <v>194</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>5354</v>
       </c>
-      <c r="I62">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J62">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>32</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="s">
+        <v>52</v>
+      </c>
+      <c r="C63">
         <v>253</v>
       </c>
-      <c r="C63">
-        <v>8</v>
-      </c>
       <c r="D63">
+        <v>8</v>
+      </c>
+      <c r="E63">
         <v>339.15602999999999</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
         <v>857</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>220920</v>
       </c>
-      <c r="I63">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J63">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>33</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="s">
+        <v>52</v>
+      </c>
+      <c r="C64">
         <v>367</v>
       </c>
-      <c r="C64">
-        <v>8</v>
-      </c>
       <c r="D64">
+        <v>8</v>
+      </c>
+      <c r="E64">
         <v>5036.56538</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>2</v>
       </c>
       <c r="G64">
+        <v>2</v>
+      </c>
+      <c r="H64">
         <v>810</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>263543</v>
       </c>
-      <c r="I64">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J64">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>34</v>
       </c>
-      <c r="B65">
+      <c r="B65" t="s">
+        <v>52</v>
+      </c>
+      <c r="C65">
         <v>263</v>
       </c>
-      <c r="C65">
-        <v>8</v>
-      </c>
       <c r="D65">
+        <v>8</v>
+      </c>
+      <c r="E65">
         <v>-2269.4554499999999</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>0</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
       <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
         <v>258</v>
       </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>35</v>
       </c>
-      <c r="B66">
+      <c r="B66" t="s">
+        <v>52</v>
+      </c>
+      <c r="C66">
         <v>263</v>
       </c>
-      <c r="C66">
-        <v>8</v>
-      </c>
       <c r="D66">
+        <v>8</v>
+      </c>
+      <c r="E66">
         <v>-2215.1211199999998</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>0</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
         <v>258</v>
       </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>36</v>
       </c>
-      <c r="B67">
+      <c r="B67" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67">
         <v>253</v>
       </c>
-      <c r="C67">
-        <v>8</v>
-      </c>
       <c r="D67">
+        <v>8</v>
+      </c>
+      <c r="E67">
         <v>-324.54599000000002</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>0</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
         <v>8948</v>
       </c>
-      <c r="I67">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J67">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>37</v>
       </c>
-      <c r="B68">
+      <c r="B68" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68">
         <v>253</v>
       </c>
-      <c r="C68">
-        <v>8</v>
-      </c>
       <c r="D68">
+        <v>8</v>
+      </c>
+      <c r="E68">
         <v>-249.32962000000001</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>0</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
         <v>8102</v>
       </c>
-      <c r="I68">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J68">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>38</v>
       </c>
-      <c r="B69">
+      <c r="B69" t="s">
+        <v>52</v>
+      </c>
+      <c r="C69">
         <v>253</v>
       </c>
-      <c r="C69">
-        <v>8</v>
-      </c>
       <c r="D69">
+        <v>8</v>
+      </c>
+      <c r="E69">
         <v>-198.5247</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>0</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
         <v>3210</v>
       </c>
-      <c r="I69">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>39</v>
       </c>
-      <c r="B70">
+      <c r="B70" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70">
         <v>263</v>
       </c>
-      <c r="C70">
-        <v>8</v>
-      </c>
       <c r="D70">
+        <v>8</v>
+      </c>
+      <c r="E70">
         <v>-2038.3657800000001</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>0</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
         <v>258</v>
       </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>40</v>
       </c>
-      <c r="B71">
+      <c r="B71" t="s">
+        <v>52</v>
+      </c>
+      <c r="C71">
         <v>253</v>
       </c>
-      <c r="C71">
-        <v>8</v>
-      </c>
       <c r="D71">
+        <v>8</v>
+      </c>
+      <c r="E71">
         <v>169.3253</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>0</v>
       </c>
       <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
         <v>1058</v>
       </c>
-      <c r="H71">
+      <c r="I71">
         <v>215718</v>
       </c>
-      <c r="I71">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J71">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>41</v>
       </c>
-      <c r="B72">
+      <c r="B72" t="s">
+        <v>52</v>
+      </c>
+      <c r="C72">
         <v>253</v>
       </c>
-      <c r="C72">
-        <v>8</v>
-      </c>
       <c r="D72">
+        <v>8</v>
+      </c>
+      <c r="E72">
         <v>125.98056</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>0</v>
       </c>
       <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
         <v>1040</v>
       </c>
-      <c r="H72">
+      <c r="I72">
         <v>310517</v>
       </c>
-      <c r="I72">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J72">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>42</v>
       </c>
-      <c r="B73">
+      <c r="B73" t="s">
+        <v>52</v>
+      </c>
+      <c r="C73">
         <v>253</v>
       </c>
-      <c r="C73">
-        <v>8</v>
-      </c>
       <c r="D73">
+        <v>8</v>
+      </c>
+      <c r="E73">
         <v>193.62531999999999</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>0</v>
       </c>
       <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
         <v>1103</v>
       </c>
-      <c r="H73">
+      <c r="I73">
         <v>276101</v>
       </c>
-      <c r="I73">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J73">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>43</v>
       </c>
-      <c r="B74">
+      <c r="B74" t="s">
+        <v>52</v>
+      </c>
+      <c r="C74">
         <v>253</v>
       </c>
-      <c r="C74">
-        <v>8</v>
-      </c>
       <c r="D74">
+        <v>8</v>
+      </c>
+      <c r="E74">
         <v>-321.84192000000002</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>0</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
       <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
         <v>3631</v>
       </c>
-      <c r="I74">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J74">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>44</v>
       </c>
-      <c r="B75">
+      <c r="B75" t="s">
+        <v>52</v>
+      </c>
+      <c r="C75">
         <v>263</v>
       </c>
-      <c r="C75">
-        <v>8</v>
-      </c>
       <c r="D75">
+        <v>8</v>
+      </c>
+      <c r="E75">
         <v>-50.432040000000001</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>0</v>
       </c>
       <c r="G75">
         <v>0</v>
       </c>
       <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
         <v>2896</v>
       </c>
-      <c r="I75">
+      <c r="J75">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R75">
-    <sortCondition ref="C8:C75"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S75">
+    <sortCondition ref="D8:D75"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
